--- a/docs/kakao-logging-plan.xlsx
+++ b/docs/kakao-logging-plan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="511">
   <si>
     <t xml:space="preserve">카카오 광고 자가 진단 — 로그 수집 설계</t>
   </si>
@@ -279,7 +279,82 @@
     <t xml:space="preserve">리포트 목록</t>
   </si>
   <si>
-    <t xml:space="preserve">믹스패널에서 볼 수 있는 리포트와 볼 수 없는 것</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만들 리포트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(01~05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름 규칙 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">볼 수 없는 것</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2602,6 +2677,143 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">},
+    selected_options: [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객 행동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객행동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 문제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재문제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}],
     recommended_ads: [{</t>
     </r>
     <r>
@@ -5093,6 +5305,143 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">},
+    selected_options: [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객 행동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객행동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 문제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재문제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Courier New"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}],
     recommended_ads: [{</t>
     </r>
     <r>
@@ -8035,81 +8384,572 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보고 싶은 것</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리포트 종류</t>
-  </si>
-  <si>
-    <t xml:space="preserve">믹스패널 설정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요청 여부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">각 버튼별 클릭수</t>
+    <t xml:space="preserve">리포트 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종류</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Event / </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무엇을 답하나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우선순위</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과별 업종 집계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Insights · Table</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">result_type → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그 아래 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">industry (2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단 중첩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">is_internal is not true</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가지 결과와 횟수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">각 결과를 받은 업종 내역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자식 행 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부모 행</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">먼저</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택지별 선택 수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_options</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 선택지 전체 순위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">진단 완료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건당 각 항목 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버튼별 클릭 수</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Insights · Bar</t>
   </si>
   <si>
-    <t xml:space="preserve">click@button → Breakdown object_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요청</t>
-  </si>
-  <si>
-    <t xml:space="preserve">유형별 광고 가이드 확인률</t>
+    <t xml:space="preserve">어느 버튼이 얼마나 눌렸나</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유형별 가이드 확인률</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Funnels</t>
   </si>
   <si>
-    <t xml:space="preserve">pageview@result → click@button(open_guide) → click@link(custom_guide), Breakdown result_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">유형별 스타터 키트 확인률</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위와 동일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마지막 단계 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">object_id=starter_kit</t>
-    </r>
-  </si>
-  <si>
+    <t xml:space="preserve">pageview@result → click@button → click@link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">result_type</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">object_id=open_guide / 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">object_id=custom_guide</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">결과를 받고 가이드를 실제로 열어보나</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">진단 완주율</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">pageview@intro → pageview@diagnosis_question → pageview@result</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시작한 사람 중 몇 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 끝까지 하나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과별 현재 문제 집계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">result_type → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그 아래 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">situation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번의 업종 자리를 현재 문제로 바꾼 것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장 없이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번에서 바꿔 봐도 됨</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">나중</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 조합별 진단 완료 수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">result_combo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 선택을 한 줄로 합친 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8125,14 +8965,50 @@
         <rFont val="나눔고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가지 조합별 발생 횟수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Insights · Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pageview@result → Breakdown result_combo</t>
+      <t xml:space="preserve">행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수백 건 쌓인 뒤에 의미 있음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가이드별 이동 수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">guide_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">object_id=custom_guide</t>
   </si>
   <si>
     <r>
@@ -8150,13 +9026,46 @@
         <rFont val="나눔고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가지 결과별 발생 횟수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">pageview@result → Breakdown result_type</t>
-  </si>
-  <si>
+      <t xml:space="preserve">종 가이드 중 어디로 많이 갔나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스텝별 이탈</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번 퍼널을 스텝 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8172,38 +9081,355 @@
         <rFont val="나눔고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">스텝 선택지별 선택 횟수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">pageview@result → Breakdown industry / path / situation / goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">선택지를 바꿔 고른 횟수</t>
+      <t xml:space="preserve">개로 펼침</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 질문에서 나가나</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과 저장률</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">pageview@result → click@button(open_download) → click@button(download_png/pdf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결과를 저장해 가나</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택지 변경 횟수</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Insights</t>
   </si>
   <si>
-    <t xml:space="preserve">select@option → Filter is_change=true → Breakdown step</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">어떤 가이드가 많이 열렸나 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
+    <t xml:space="preserve">is_change=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 질문에서 망설이나</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유입 채널별 완주율</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번 퍼널 복제</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 채널 유입이 끝까지 하나</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장 형식 선호</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Insights · Pie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">object_id in (download_png, download_pdf)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이미지와 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중 무엇을 고르나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장 실패 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장애</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">error@button, error@screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">error_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저장이 실패하거나 화면이 깨지나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이름 규칙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">형식</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번호 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무엇 기준으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무슨 수치</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">추천 유형</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">result_type · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객 행동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추천 광고가 갈리는 기준</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 조합</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">result_combo · 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 선택을 모두 합친 것 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 600</t>
     </r>
     <r>
       <rPr>
@@ -8213,119 +9439,82 @@
       </rPr>
       <t xml:space="preserve">종</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">click@link + object_id=custom_guide → Breakdown guide_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체 완주율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pageview@intro → STEP1~4 → pageview@result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">어느 질문에서 이탈하나</t>
-  </si>
-  <si>
-    <t xml:space="preserve">위 퍼널의 단계별 전환율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결과 저장률</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pageview@result → click(open_download) → click(download_png/pdf)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PNG vs PDF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선호</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Insights · Pie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click@button → Filter object_id in (download_png, download_pdf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">유입 채널별 성과</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">완주 퍼널 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Breakdown utm_source</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">결과를 끝까지 읽었나</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scroll@section → Breakdown object_id (section_01~04)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장 실패율 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장애</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">error@button, error@screen → Breakdown error_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선택지</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">selected_options · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고른 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개를 목록 한 칸에 담은 것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항목별로 세어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">행</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">주의</t>
   </si>
   <si>
     <r>
@@ -8336,7 +9525,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Custom Event (</t>
+      <t xml:space="preserve">"</t>
     </r>
     <r>
       <rPr>
@@ -8345,7 +9534,7 @@
         <rFont val="나눔고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">믹스패널 화면에서 설정</t>
+      <t xml:space="preserve">결과</t>
     </r>
     <r>
       <rPr>
@@ -8355,7 +9544,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">" </t>
     </r>
     <r>
       <rPr>
@@ -8364,57 +9553,307 @@
         <rFont val="나눔고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">코드 변경 없음</t>
-    </r>
+      <t xml:space="preserve">라는 말은 두 가지를 다 가리켜 혼동되므로 쓰지 않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번을 이렇게 만드는 이유</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고객 행동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과 이름에 이미 들어있어 항상 부모와 같은 수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">따로 볼 필요 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 문제</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 결과를 받아도 사람마다 다름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그래서 자식 행으로 쪼개짐</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">좌우 배치</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">이름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정의</t>
-  </si>
-  <si>
-    <t xml:space="preserve">진단 시작</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click@button + object_id = start_diagnosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결과 도달</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광고 가이드 열기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click@button + object_id = open_guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가이드 링크 클릭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click@link + object_id in (custom_guide, starter_kit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결과 저장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click@button + object_id in (download_png, download_pdf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다시 테스트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">click@button + object_id = restart</t>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">믹스패널은 위아래 중첩만 됨</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종과 현재 문제를 나란히 두는 것은 불가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Free </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">플랜 제약</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">저장 리포트</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">좌석당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01~05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 먼저 저장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">저장 안 한 리포트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개수에 안 들어감</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Breakdown </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 바꿔 보는 것은 무제한</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">좌석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무제한</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Analyst </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 초대하면 그 사람 몫 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개가 추가됨</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">볼 수 없는 것</t>
@@ -8640,7 +10079,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -8652,7 +10091,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">외부 서비스라 우리 로그가 닿지 않음</t>
+    <t xml:space="preserve">외부 서비스라 우리 스크립트가 닿지 않음</t>
   </si>
   <si>
     <r>
@@ -10011,7 +11450,7 @@
       </c>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>150</v>
       </c>
@@ -11050,7 +12489,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>150</v>
       </c>
@@ -12492,460 +13931,669 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="7.2421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="66.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>405</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>410</v>
       </c>
+      <c r="G1" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>413</v>
+      </c>
       <c r="C2" s="6" t="s">
-        <v>411</v>
+        <v>243</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="E2" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>414</v>
-      </c>
       <c r="C3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="F7" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C8" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C9" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>431</v>
-      </c>
       <c r="C10" s="6" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>432</v>
+        <v>263</v>
       </c>
       <c r="E10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>433</v>
+      <c r="F10" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>434</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
+      <c r="F11" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>435</v>
+      <c r="A12" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>415</v>
+        <v>238</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
+      <c r="A13" s="6" t="s">
+        <v>454</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>439</v>
+        <v>320</v>
       </c>
       <c r="E13" s="3"/>
+      <c r="F13" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>440</v>
+      <c r="A14" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>458</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>234</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>442</v>
+      <c r="A15" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="E15" s="3"/>
+      <c r="F15" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="E16" s="3"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
+      <c r="A17" s="5" t="s">
+        <v>465</v>
+      </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>448</v>
+        <v>468</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>469</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>243</v>
+        <v>473</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>455</v>
-      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>457</v>
-      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>459</v>
+        <v>477</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>478</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>480</v>
+      </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>482</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>463</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>466</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>468</v>
+        <v>485</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>486</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-    </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>477</v>
-      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
